--- a/facility_management_forms/008_facility_management_modernization_survey--facility_management_forms.xlsx
+++ b/facility_management_forms/008_facility_management_modernization_survey--facility_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'technology',_'label':_'technology',_'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'technology', 'label': 'Technology', 'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'policy',_'label':_'policy',_'value':_'policy'}</t>
+          <t>policy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'policy', 'label': 'Policy', 'value': 'Policy'}</t>
+          <t>Policy</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'people',_'label':_'people',_'value':_'people'}</t>
+          <t>people</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'people', 'label': 'People', 'value': 'People'}</t>
+          <t>People</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high',_'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'high', 'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medium', 'label': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low',_'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'low', 'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'human',_'label':_'human',_'value':_'human'}</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'human', 'label': 'Human', 'value': 'Human'}</t>
+          <t>Human</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'equipment',_'label':_'equipment',_'value':_'equipment'}</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'equipment', 'label': 'Equipment', 'value': 'Equipment'}</t>
+          <t>Equipment</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'technology',_'label':_'technology',_'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'technology', 'label': 'Technology', 'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'automation',_'label':_'automation',_'value':_'automation'}</t>
+          <t>automation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'automation', 'label': 'Automation', 'value': 'Automation'}</t>
+          <t>Automation</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'artificial_intelligence',_'label':_'artificial_intelligence',_'value':_'artificial_intelligence'}</t>
+          <t>artificial_intelligence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'artificial_intelligence', 'label': 'Artificial Intelligence', 'value': 'Artificial Intelligence'}</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'robotics',_'label':_'robotics',_'value':_'robotics'}</t>
+          <t>robotics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'robotics', 'label': 'Robotics', 'value': 'Robotics'}</t>
+          <t>Robotics</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'virtualization',_'label':_'virtualization',_'value':_'virtualization'}</t>
+          <t>virtualization</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'virtualization', 'label': 'Virtualization', 'value': 'Virtualization'}</t>
+          <t>Virtualization</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'financial',_'label':_'financial',_'value':_'financial'}</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'financial', 'label': 'Financial', 'value': 'Financial'}</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'regulatory',_'label':_'regulatory',_'value':_'regulatory'}</t>
+          <t>regulatory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'regulatory', 'label': 'Regulatory', 'value': 'Regulatory'}</t>
+          <t>Regulatory</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'reputational',_'label':_'reputational',_'value':_'reputational'}</t>
+          <t>reputational</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'reputational', 'label': 'Reputational', 'value': 'Reputational'}</t>
+          <t>Reputational</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'operational',_'label':_'operational',_'value':_'operational'}</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'operational', 'label': 'Operational', 'value': 'Operational'}</t>
+          <t>Operational</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'technological',_'label':_'technological',_'value':_'technological'}</t>
+          <t>technological</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'technological', 'label': 'Technological', 'value': 'Technological'}</t>
+          <t>Technological</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'ongoing',_'label':_'ongoing',_'value':_'ongoing'}</t>
+          <t>ongoing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'ongoing', 'label': 'Ongoing', 'value': 'Ongoing'}</t>
+          <t>Ongoing</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'completed',_'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'completed', 'label': 'Completed', 'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cancelled',_'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'cancelled', 'label': 'Cancelled', 'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'not_starting',_'label':_'not_starting',_'value':_'not_starting'}</t>
+          <t>not_starting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'not_starting', 'label': 'Not Starting', 'value': 'Not Starting'}</t>
+          <t>Not Starting</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'human',_'label':_'human',_'value':_'human'}</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'human', 'label': 'Human', 'value': 'Human'}</t>
+          <t>Human</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'equipment',_'label':_'equipment',_'value':_'equipment'}</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'equipment', 'label': 'Equipment', 'value': 'Equipment'}</t>
+          <t>Equipment</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'technology',_'label':_'technology',_'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'technology', 'label': 'Technology', 'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'automation',_'label':_'automation',_'value':_'automation'}</t>
+          <t>automation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'automation', 'label': 'Automation', 'value': 'Automation'}</t>
+          <t>Automation</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'artificial_intelligence',_'label':_'artificial_intelligence',_'value':_'artificial_intelligence'}</t>
+          <t>artificial_intelligence</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'artificial_intelligence', 'label': 'Artificial Intelligence', 'value': 'Artificial Intelligence'}</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'robotics',_'label':_'robotics',_'value':_'robotics'}</t>
+          <t>robotics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'robotics', 'label': 'Robotics', 'value': 'Robotics'}</t>
+          <t>Robotics</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'virtualization',_'label':_'virtualization',_'value':_'virtualization'}</t>
+          <t>virtualization</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'virtualization', 'label': 'Virtualization', 'value': 'Virtualization'}</t>
+          <t>Virtualization</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'financial',_'label':_'financial',_'value':_'financial'}</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'financial', 'label': 'Financial', 'value': 'Financial'}</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'regulatory',_'label':_'regulatory',_'value':_'regulatory'}</t>
+          <t>regulatory</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'regulatory', 'label': 'Regulatory', 'value': 'Regulatory'}</t>
+          <t>Regulatory</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'reputational',_'label':_'reputational',_'value':_'reputational'}</t>
+          <t>reputational</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'reputational', 'label': 'Reputational', 'value': 'Reputational'}</t>
+          <t>Reputational</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'operational',_'label':_'operational',_'value':_'operational'}</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'operational', 'label': 'Operational', 'value': 'Operational'}</t>
+          <t>Operational</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'technological',_'label':_'technological',_'value':_'technological'}</t>
+          <t>technological</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'technological', 'label': 'Technological', 'value': 'Technological'}</t>
+          <t>Technological</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'internal',_'label':_'internal',_'value':_'internal'}</t>
+          <t>internal</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'internal', 'label': 'Internal', 'value': 'Internal'}</t>
+          <t>Internal</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'external',_'label':_'external',_'value':_'external'}</t>
+          <t>external</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'external', 'label': 'External', 'value': 'External'}</t>
+          <t>External</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'contractor',_'label':_'contractor',_'value':_'contractor'}</t>
+          <t>contractor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'contractor', 'label': 'Contractor', 'value': 'Contractor'}</t>
+          <t>Contractor</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'design',_'label':_'design',_'value':_'design'}</t>
+          <t>design</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'design', 'label': 'Design', 'value': 'Design'}</t>
+          <t>Design</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'development',_'label':_'development',_'value':_'development'}</t>
+          <t>development</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'development', 'label': 'Development', 'value': 'Development'}</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'testing',_'label':_'testing',_'value':_'testing'}</t>
+          <t>testing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'testing', 'label': 'Testing', 'value': 'Testing'}</t>
+          <t>Testing</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'deployment',_'label':_'deployment',_'value':_'deployment'}</t>
+          <t>deployment</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'deployment', 'label': 'Deployment', 'value': 'Deployment'}</t>
+          <t>Deployment</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'maintenance',_'label':_'maintenance',_'value':_'maintenance'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'maintenance', 'label': 'Maintenance', 'value': 'Maintenance'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
